--- a/data/team_stats/2025-26NBA_RegularSeason_Opponent_stats.xlsx
+++ b/data/team_stats/2025-26NBA_RegularSeason_Opponent_stats.xlsx
@@ -1621,19 +1621,19 @@
         <v>493</v>
       </c>
       <c r="J2" t="n">
-        <v>8271</v>
+        <v>8304</v>
       </c>
       <c r="K2" t="n">
-        <v>8337</v>
+        <v>8304</v>
       </c>
       <c r="L2" t="n">
-        <v>2208</v>
+        <v>2235</v>
       </c>
       <c r="M2" t="n">
-        <v>2046</v>
+        <v>2017</v>
       </c>
       <c r="N2" t="n">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="O2" t="n">
         <v>16608</v>
@@ -1981,7 +1981,7 @@
         <v>2630</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2188</v>
+        <v>2215</v>
       </c>
       <c r="EA2" t="n">
         <v>121</v>
@@ -2128,16 +2128,16 @@
         <v>0.5506912442396313</v>
       </c>
       <c r="FW2" t="n">
-        <v>14.53754080522307</v>
+        <v>14.47976878612717</v>
       </c>
       <c r="FX2" t="n">
-        <v>13.97625044980209</v>
+        <v>14.03179190751445</v>
       </c>
       <c r="FY2" t="n">
-        <v>13.88786120178938</v>
+        <v>13.83267100192678</v>
       </c>
       <c r="FZ2" t="n">
-        <v>13.3547319179561</v>
+        <v>13.40780346820809</v>
       </c>
       <c r="GA2" t="n">
         <v>0.2959306204136091</v>
@@ -2281,7 +2281,7 @@
         <v>25.30777988614801</v>
       </c>
       <c r="HV2" t="n">
-        <v>0.2669568371418208</v>
+        <v>0.2691473988439306</v>
       </c>
     </row>
     <row r="3">
@@ -2325,19 +2325,19 @@
         <v>655</v>
       </c>
       <c r="J3" t="n">
-        <v>8287</v>
+        <v>8323</v>
       </c>
       <c r="K3" t="n">
-        <v>8356</v>
+        <v>8320</v>
       </c>
       <c r="L3" t="n">
-        <v>2336</v>
+        <v>2364</v>
       </c>
       <c r="M3" t="n">
-        <v>2172</v>
+        <v>2149</v>
       </c>
       <c r="N3" t="n">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="O3" t="n">
         <v>16643</v>
@@ -2683,7 +2683,7 @@
         <v>2756</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2322</v>
+        <v>2350</v>
       </c>
       <c r="EA3" t="n">
         <v>142</v>
@@ -2830,16 +2830,16 @@
         <v>0.5923076923076923</v>
       </c>
       <c r="FW3" t="n">
-        <v>14.52304814770122</v>
+        <v>14.4602306860507</v>
       </c>
       <c r="FX3" t="n">
-        <v>13.96691000478698</v>
+        <v>14.02734375</v>
       </c>
       <c r="FY3" t="n">
-        <v>13.95626885483287</v>
+        <v>13.89590291962033</v>
       </c>
       <c r="FZ3" t="n">
-        <v>13.46443274293921</v>
+        <v>13.52269230769231</v>
       </c>
       <c r="GA3" t="n">
         <v>0.3102801233078676</v>
@@ -2983,7 +2983,7 @@
         <v>25.8100214745884</v>
       </c>
       <c r="HV3" t="n">
-        <v>0.2818872933510317</v>
+        <v>0.2840321999279106</v>
       </c>
     </row>
     <row r="4">
@@ -3027,19 +3027,19 @@
         <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>8278</v>
+        <v>8309</v>
       </c>
       <c r="K4" t="n">
-        <v>8343</v>
+        <v>8312</v>
       </c>
       <c r="L4" t="n">
-        <v>2117</v>
+        <v>2142</v>
       </c>
       <c r="M4" t="n">
-        <v>2281</v>
+        <v>2259</v>
       </c>
       <c r="N4" t="n">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="O4" t="n">
         <v>16621</v>
@@ -3387,7 +3387,7 @@
         <v>2407</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2090</v>
+        <v>2115</v>
       </c>
       <c r="EA4" t="n">
         <v>163</v>
@@ -3534,16 +3534,16 @@
         <v>0.5970149253731343</v>
       </c>
       <c r="FW4" t="n">
-        <v>14.41346943706209</v>
+        <v>14.35969430737754</v>
       </c>
       <c r="FX4" t="n">
-        <v>14.11306484478006</v>
+        <v>14.16570019249278</v>
       </c>
       <c r="FY4" t="n">
-        <v>13.80498912780865</v>
+        <v>13.75348417378746</v>
       </c>
       <c r="FZ4" t="n">
-        <v>13.32313316552799</v>
+        <v>13.37282242540905</v>
       </c>
       <c r="GA4" t="n">
         <v>0.2816576086956522</v>
@@ -3687,7 +3687,7 @@
         <v>25.40543743464622</v>
       </c>
       <c r="HV4" t="n">
-        <v>0.2557381009905774</v>
+        <v>0.2577927548441449</v>
       </c>
     </row>
     <row r="5">
@@ -3731,19 +3731,19 @@
         <v>-275</v>
       </c>
       <c r="J5" t="n">
-        <v>8280</v>
+        <v>8299</v>
       </c>
       <c r="K5" t="n">
-        <v>8334</v>
+        <v>8315</v>
       </c>
       <c r="L5" t="n">
-        <v>2338</v>
+        <v>2355</v>
       </c>
       <c r="M5" t="n">
-        <v>2179</v>
+        <v>2159</v>
       </c>
       <c r="N5" t="n">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="O5" t="n">
         <v>16614</v>
@@ -4091,7 +4091,7 @@
         <v>2738</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2314</v>
+        <v>2331</v>
       </c>
       <c r="EA5" t="n">
         <v>154</v>
@@ -4238,16 +4238,16 @@
         <v>0.606508875739645</v>
       </c>
       <c r="FW5" t="n">
-        <v>14.42851449275362</v>
+        <v>14.39548138329919</v>
       </c>
       <c r="FX5" t="n">
-        <v>14.14589632829374</v>
+        <v>14.17822008418521</v>
       </c>
       <c r="FY5" t="n">
-        <v>13.80022946859903</v>
+        <v>13.76863477527413</v>
       </c>
       <c r="FZ5" t="n">
-        <v>13.55659947204224</v>
+        <v>13.58757666867108</v>
       </c>
       <c r="GA5" t="n">
         <v>0.3081922816519973</v>
@@ -4391,7 +4391,7 @@
         <v>25.24985642498206</v>
       </c>
       <c r="HV5" t="n">
-        <v>0.2823671497584541</v>
+        <v>0.2837691288107001</v>
       </c>
     </row>
     <row r="6">
@@ -4435,19 +4435,19 @@
         <v>-422</v>
       </c>
       <c r="J6" t="n">
-        <v>8169</v>
+        <v>8201</v>
       </c>
       <c r="K6" t="n">
-        <v>8234</v>
+        <v>8202</v>
       </c>
       <c r="L6" t="n">
-        <v>1883</v>
+        <v>1911</v>
       </c>
       <c r="M6" t="n">
-        <v>2377</v>
+        <v>2352</v>
       </c>
       <c r="N6" t="n">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="O6" t="n">
         <v>16403</v>
@@ -4795,7 +4795,7 @@
         <v>2211</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1864</v>
+        <v>1892</v>
       </c>
       <c r="EA6" t="n">
         <v>204</v>
@@ -4942,16 +4942,16 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="FW6" t="n">
-        <v>14.37780634104542</v>
+        <v>14.32170467016218</v>
       </c>
       <c r="FX6" t="n">
-        <v>14.78111488948263</v>
+        <v>14.838783223604</v>
       </c>
       <c r="FY6" t="n">
-        <v>13.83319867792876</v>
+        <v>13.77922204609194</v>
       </c>
       <c r="FZ6" t="n">
-        <v>14.29160796696624</v>
+        <v>14.34736649597659</v>
       </c>
       <c r="GA6" t="n">
         <v>0.2573099415204678</v>
@@ -5095,7 +5095,7 @@
         <v>25.46892144638404</v>
       </c>
       <c r="HV6" t="n">
-        <v>0.2305055698371894</v>
+        <v>0.2330203633703207</v>
       </c>
     </row>
     <row r="7">
@@ -5139,19 +5139,19 @@
         <v>-232</v>
       </c>
       <c r="J7" t="n">
-        <v>8088</v>
+        <v>8119</v>
       </c>
       <c r="K7" t="n">
-        <v>8148</v>
+        <v>8117</v>
       </c>
       <c r="L7" t="n">
-        <v>2301</v>
+        <v>2328</v>
       </c>
       <c r="M7" t="n">
-        <v>2049</v>
+        <v>2022</v>
       </c>
       <c r="N7" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="O7" t="n">
         <v>16236</v>
@@ -5497,7 +5497,7 @@
         <v>2541</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2294</v>
+        <v>2321</v>
       </c>
       <c r="EA7" t="n">
         <v>109</v>
@@ -5644,16 +5644,16 @@
         <v>0.5790754257907542</v>
       </c>
       <c r="FW7" t="n">
-        <v>15.10964391691395</v>
+        <v>15.05195221086341</v>
       </c>
       <c r="FX7" t="n">
-        <v>14.13269513991163</v>
+        <v>14.18666995195269</v>
       </c>
       <c r="FY7" t="n">
-        <v>14.51287091988131</v>
+        <v>14.45745781500185</v>
       </c>
       <c r="FZ7" t="n">
-        <v>13.53527245949926</v>
+        <v>13.58696562769496</v>
       </c>
       <c r="GA7" t="n">
         <v>0.2999151583710407</v>
@@ -5797,7 +5797,7 @@
         <v>25.74916808149406</v>
       </c>
       <c r="HV7" t="n">
-        <v>0.2844955489614243</v>
+        <v>0.286734819559059</v>
       </c>
     </row>
     <row r="8">
@@ -5841,19 +5841,19 @@
         <v>-93</v>
       </c>
       <c r="J8" t="n">
-        <v>7921</v>
+        <v>7958</v>
       </c>
       <c r="K8" t="n">
-        <v>7991</v>
+        <v>7954</v>
       </c>
       <c r="L8" t="n">
-        <v>1791</v>
+        <v>1820</v>
       </c>
       <c r="M8" t="n">
-        <v>2177</v>
+        <v>2148</v>
       </c>
       <c r="N8" t="n">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="O8" t="n">
         <v>15912</v>
@@ -6201,7 +6201,7 @@
         <v>2169</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1780</v>
+        <v>1809</v>
       </c>
       <c r="EA8" t="n">
         <v>149</v>
@@ -6348,16 +6348,16 @@
         <v>0.6127320954907162</v>
       </c>
       <c r="FW8" t="n">
-        <v>14.70646383032445</v>
+        <v>14.63808745916059</v>
       </c>
       <c r="FX8" t="n">
-        <v>15.12577900137655</v>
+        <v>15.19614030676389</v>
       </c>
       <c r="FY8" t="n">
-        <v>14.00781466986492</v>
+        <v>13.94268660467454</v>
       </c>
       <c r="FZ8" t="n">
-        <v>14.62597922662996</v>
+        <v>14.69401558964043</v>
       </c>
       <c r="GA8" t="n">
         <v>0.2590436590436591</v>
@@ -6501,7 +6501,7 @@
         <v>25.74313922356091</v>
       </c>
       <c r="HV8" t="n">
-        <v>0.2261078146698649</v>
+        <v>0.2287006785624529</v>
       </c>
     </row>
     <row r="9">
@@ -6545,19 +6545,19 @@
         <v>-396</v>
       </c>
       <c r="J9" t="n">
-        <v>7949</v>
+        <v>7983</v>
       </c>
       <c r="K9" t="n">
-        <v>8028</v>
+        <v>7994</v>
       </c>
       <c r="L9" t="n">
-        <v>1786</v>
+        <v>1810</v>
       </c>
       <c r="M9" t="n">
-        <v>2056</v>
+        <v>2030</v>
       </c>
       <c r="N9" t="n">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="O9" t="n">
         <v>15977</v>
@@ -6903,7 +6903,7 @@
         <v>1959</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1773</v>
+        <v>1797</v>
       </c>
       <c r="EA9" t="n">
         <v>146</v>
@@ -7050,16 +7050,16 @@
         <v>0.5631868131868132</v>
       </c>
       <c r="FW9" t="n">
-        <v>14.42517297773305</v>
+        <v>14.36373543780534</v>
       </c>
       <c r="FX9" t="n">
-        <v>15.24592675635277</v>
+        <v>15.31077057793345</v>
       </c>
       <c r="FY9" t="n">
-        <v>13.83678450119512</v>
+        <v>13.77785293749217</v>
       </c>
       <c r="FZ9" t="n">
-        <v>14.39260089686099</v>
+        <v>14.45381536152114</v>
       </c>
       <c r="GA9" t="n">
         <v>0.2855761260016579</v>
@@ -7203,7 +7203,7 @@
         <v>25.66545827633379</v>
       </c>
       <c r="HV9" t="n">
-        <v>0.2246823499811297</v>
+        <v>0.2267318050858073</v>
       </c>
     </row>
     <row r="10">
@@ -7247,19 +7247,19 @@
         <v>983</v>
       </c>
       <c r="J10" t="n">
-        <v>8355</v>
+        <v>8390</v>
       </c>
       <c r="K10" t="n">
-        <v>8424</v>
+        <v>8389</v>
       </c>
       <c r="L10" t="n">
-        <v>2539</v>
+        <v>2571</v>
       </c>
       <c r="M10" t="n">
-        <v>1893</v>
+        <v>1863</v>
       </c>
       <c r="N10" t="n">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="O10" t="n">
         <v>16779</v>
@@ -7605,7 +7605,7 @@
         <v>3055</v>
       </c>
       <c r="DZ10" t="n">
-        <v>2530</v>
+        <v>2562</v>
       </c>
       <c r="EA10" t="n">
         <v>128</v>
@@ -7752,16 +7752,16 @@
         <v>0.5730337078651685</v>
       </c>
       <c r="FW10" t="n">
-        <v>14.18269299820467</v>
+        <v>14.12352800953516</v>
       </c>
       <c r="FX10" t="n">
-        <v>14.07450142450143</v>
+        <v>14.13322207652879</v>
       </c>
       <c r="FY10" t="n">
-        <v>13.53979652902454</v>
+        <v>13.48331346841478</v>
       </c>
       <c r="FZ10" t="n">
-        <v>13.55557929724596</v>
+        <v>13.61213493861009</v>
       </c>
       <c r="GA10" t="n">
         <v>0.3287960882780494</v>
@@ -7905,7 +7905,7 @@
         <v>25.85679133858268</v>
       </c>
       <c r="HV10" t="n">
-        <v>0.3038898862956314</v>
+        <v>0.3064362336114422</v>
       </c>
     </row>
     <row r="11">
@@ -7949,19 +7949,19 @@
         <v>820</v>
       </c>
       <c r="J11" t="n">
-        <v>8156</v>
+        <v>8196</v>
       </c>
       <c r="K11" t="n">
-        <v>8211</v>
+        <v>8171</v>
       </c>
       <c r="L11" t="n">
-        <v>2025</v>
+        <v>2058</v>
       </c>
       <c r="M11" t="n">
-        <v>1851</v>
+        <v>1821</v>
       </c>
       <c r="N11" t="n">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="O11" t="n">
         <v>16367</v>
@@ -8309,7 +8309,7 @@
         <v>2430</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2002</v>
+        <v>2035</v>
       </c>
       <c r="EA11" t="n">
         <v>109</v>
@@ -8456,16 +8456,16 @@
         <v>0.6321243523316062</v>
       </c>
       <c r="FW11" t="n">
-        <v>14.38662334477685</v>
+        <v>14.31641044411908</v>
       </c>
       <c r="FX11" t="n">
-        <v>14.58076969918402</v>
+        <v>14.65214783992167</v>
       </c>
       <c r="FY11" t="n">
-        <v>13.76836684649338</v>
+        <v>13.70117130307467</v>
       </c>
       <c r="FZ11" t="n">
-        <v>13.94722932651321</v>
+        <v>14.01550605801003</v>
       </c>
       <c r="GA11" t="n">
         <v>0.2397652838427947</v>
@@ -8609,7 +8609,7 @@
         <v>25.74266131728519</v>
       </c>
       <c r="HV11" t="n">
-        <v>0.2482834722903384</v>
+        <v>0.2510980966325037</v>
       </c>
     </row>
     <row r="12">
@@ -8653,19 +8653,19 @@
         <v>369</v>
       </c>
       <c r="J12" t="n">
-        <v>8278</v>
+        <v>8315</v>
       </c>
       <c r="K12" t="n">
-        <v>8347</v>
+        <v>8310</v>
       </c>
       <c r="L12" t="n">
-        <v>2037</v>
+        <v>2065</v>
       </c>
       <c r="M12" t="n">
-        <v>2295</v>
+        <v>2263</v>
       </c>
       <c r="N12" t="n">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="O12" t="n">
         <v>16625</v>
@@ -9011,7 +9011,7 @@
         <v>2399</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2010</v>
+        <v>2038</v>
       </c>
       <c r="EA12" t="n">
         <v>134</v>
@@ -9158,16 +9158,16 @@
         <v>0.6302521008403361</v>
       </c>
       <c r="FW12" t="n">
-        <v>14.40065233148104</v>
+        <v>14.3365724594107</v>
       </c>
       <c r="FX12" t="n">
-        <v>14.19089493231101</v>
+        <v>14.25407942238267</v>
       </c>
       <c r="FY12" t="n">
-        <v>13.78128775066441</v>
+        <v>13.71996392062537</v>
       </c>
       <c r="FZ12" t="n">
-        <v>13.63461123757038</v>
+        <v>13.69531889290012</v>
       </c>
       <c r="GA12" t="n">
         <v>0.3054930509596294</v>
@@ -9311,7 +9311,7 @@
         <v>25.41239843514896</v>
       </c>
       <c r="HV12" t="n">
-        <v>0.2460739309011839</v>
+        <v>0.2483463619963921</v>
       </c>
     </row>
     <row r="13">
@@ -9355,19 +9355,19 @@
         <v>-669</v>
       </c>
       <c r="J13" t="n">
-        <v>8154</v>
+        <v>8186</v>
       </c>
       <c r="K13" t="n">
-        <v>8219</v>
+        <v>8187</v>
       </c>
       <c r="L13" t="n">
-        <v>2514</v>
+        <v>2542</v>
       </c>
       <c r="M13" t="n">
-        <v>2428</v>
+        <v>2402</v>
       </c>
       <c r="N13" t="n">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="O13" t="n">
         <v>16373</v>
@@ -9713,7 +9713,7 @@
         <v>2773</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2506</v>
+        <v>2534</v>
       </c>
       <c r="EA13" t="n">
         <v>173</v>
@@ -9860,16 +9860,16 @@
         <v>0.5441176470588235</v>
       </c>
       <c r="FW13" t="n">
-        <v>14.7364483688987</v>
+        <v>14.67884192523821</v>
       </c>
       <c r="FX13" t="n">
-        <v>14.2960214137973</v>
+        <v>14.35189935263222</v>
       </c>
       <c r="FY13" t="n">
-        <v>14.10717439293598</v>
+        <v>14.05202785243098</v>
       </c>
       <c r="FZ13" t="n">
-        <v>13.62047694366711</v>
+        <v>13.67371442530841</v>
       </c>
       <c r="GA13" t="n">
         <v>0.2491803278688525</v>
@@ -10013,7 +10013,7 @@
         <v>25.77203980099502</v>
       </c>
       <c r="HV13" t="n">
-        <v>0.3083149374540103</v>
+        <v>0.3105301734668947</v>
       </c>
     </row>
     <row r="14">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>237059.7</v>
+        <v>237060</v>
       </c>
       <c r="H14" t="n">
         <v>82</v>
@@ -10057,19 +10057,19 @@
         <v>509</v>
       </c>
       <c r="J14" t="n">
-        <v>8017</v>
+        <v>8051</v>
       </c>
       <c r="K14" t="n">
-        <v>8053</v>
+        <v>8019</v>
       </c>
       <c r="L14" t="n">
-        <v>1879</v>
+        <v>1905</v>
       </c>
       <c r="M14" t="n">
-        <v>1826</v>
+        <v>1800</v>
       </c>
       <c r="N14" t="n">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="O14" t="n">
         <v>16070</v>
@@ -10417,7 +10417,7 @@
         <v>2190</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1871</v>
+        <v>1897</v>
       </c>
       <c r="EA14" t="n">
         <v>119</v>
@@ -10558,22 +10558,22 @@
         <v>0.0447934845840605</v>
       </c>
       <c r="FU14" t="n">
-        <v>97.61591700318526</v>
+        <v>97.61579347000759</v>
       </c>
       <c r="FV14" t="n">
         <v>0.5647058823529412</v>
       </c>
       <c r="FW14" t="n">
-        <v>14.58758887364351</v>
+        <v>14.52602161222208</v>
       </c>
       <c r="FX14" t="n">
-        <v>14.91506270954924</v>
+        <v>14.97830153385709</v>
       </c>
       <c r="FY14" t="n">
-        <v>13.93548708993389</v>
+        <v>13.8766737051298</v>
       </c>
       <c r="FZ14" t="n">
-        <v>14.35445175710915</v>
+        <v>14.41531363012844</v>
       </c>
       <c r="GA14" t="n">
         <v>0.2723756906077348</v>
@@ -10717,7 +10717,7 @@
         <v>25.74424205001544</v>
       </c>
       <c r="HV14" t="n">
-        <v>0.2343769489834102</v>
+        <v>0.2366165693702646</v>
       </c>
     </row>
     <row r="15">
@@ -10761,19 +10761,19 @@
         <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>8229</v>
+        <v>8265</v>
       </c>
       <c r="K15" t="n">
-        <v>8293</v>
+        <v>8257</v>
       </c>
       <c r="L15" t="n">
-        <v>2179</v>
+        <v>2211</v>
       </c>
       <c r="M15" t="n">
-        <v>2156</v>
+        <v>2129</v>
       </c>
       <c r="N15" t="n">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="O15" t="n">
         <v>16522</v>
@@ -11121,7 +11121,7 @@
         <v>2571</v>
       </c>
       <c r="DZ15" t="n">
-        <v>2165</v>
+        <v>2197</v>
       </c>
       <c r="EA15" t="n">
         <v>139</v>
@@ -11268,16 +11268,16 @@
         <v>0.6</v>
       </c>
       <c r="FW15" t="n">
-        <v>14.22201968647466</v>
+        <v>14.16007259528131</v>
       </c>
       <c r="FX15" t="n">
-        <v>14.6541661642349</v>
+        <v>14.71805740583747</v>
       </c>
       <c r="FY15" t="n">
-        <v>13.538838254952</v>
+        <v>13.47986690865094</v>
       </c>
       <c r="FZ15" t="n">
-        <v>14.09099240323164</v>
+        <v>14.15242824270316</v>
       </c>
       <c r="GA15" t="n">
         <v>0.3119663911099065</v>
@@ -11421,7 +11421,7 @@
         <v>25.62887029288703</v>
       </c>
       <c r="HV15" t="n">
-        <v>0.2647952363592174</v>
+        <v>0.267513611615245</v>
       </c>
     </row>
     <row r="16">
@@ -11465,19 +11465,19 @@
         <v>452</v>
       </c>
       <c r="J16" t="n">
-        <v>8397</v>
+        <v>8432</v>
       </c>
       <c r="K16" t="n">
-        <v>8459</v>
+        <v>8424</v>
       </c>
       <c r="L16" t="n">
-        <v>1672</v>
+        <v>1698</v>
       </c>
       <c r="M16" t="n">
-        <v>2459</v>
+        <v>2434</v>
       </c>
       <c r="N16" t="n">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="O16" t="n">
         <v>16856</v>
@@ -11823,7 +11823,7 @@
         <v>1901</v>
       </c>
       <c r="DZ16" t="n">
-        <v>1655</v>
+        <v>1681</v>
       </c>
       <c r="EA16" t="n">
         <v>161</v>
@@ -11970,16 +11970,16 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="FW16" t="n">
-        <v>14.2113969274741</v>
+        <v>14.15240749525617</v>
       </c>
       <c r="FX16" t="n">
-        <v>14.05921503723844</v>
+        <v>14.1176282051282</v>
       </c>
       <c r="FY16" t="n">
-        <v>13.6146123615577</v>
+        <v>13.55810009487666</v>
       </c>
       <c r="FZ16" t="n">
-        <v>13.53005083343185</v>
+        <v>13.58626543209876</v>
       </c>
       <c r="GA16" t="n">
         <v>0.2989144481778237</v>
@@ -12123,7 +12123,7 @@
         <v>25.31939252336448</v>
       </c>
       <c r="HV16" t="n">
-        <v>0.1991187328807908</v>
+        <v>0.2013757115749526</v>
       </c>
     </row>
     <row r="17">
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>237060</v>
+        <v>237063</v>
       </c>
       <c r="H17" t="n">
         <v>82</v>
@@ -12167,19 +12167,19 @@
         <v>819</v>
       </c>
       <c r="J17" t="n">
-        <v>7939</v>
+        <v>7978</v>
       </c>
       <c r="K17" t="n">
-        <v>8018</v>
+        <v>7979</v>
       </c>
       <c r="L17" t="n">
-        <v>2182</v>
+        <v>2215</v>
       </c>
       <c r="M17" t="n">
-        <v>2042</v>
+        <v>2010</v>
       </c>
       <c r="N17" t="n">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="O17" t="n">
         <v>15957</v>
@@ -12525,7 +12525,7 @@
         <v>2618</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2167</v>
+        <v>2200</v>
       </c>
       <c r="EA17" t="n">
         <v>134</v>
@@ -12666,22 +12666,22 @@
         <v>0.04525032092426187</v>
       </c>
       <c r="FU17" t="n">
-        <v>96.92938496583143</v>
+        <v>96.92815833765708</v>
       </c>
       <c r="FV17" t="n">
         <v>0.6009174311926605</v>
       </c>
       <c r="FW17" t="n">
-        <v>14.69133392114876</v>
+        <v>14.61989220355979</v>
       </c>
       <c r="FX17" t="n">
-        <v>15.01939386380644</v>
+        <v>15.09280611605464</v>
       </c>
       <c r="FY17" t="n">
-        <v>14.07784355712306</v>
+        <v>14.00940085234395</v>
       </c>
       <c r="FZ17" t="n">
-        <v>14.46237216263407</v>
+        <v>14.53306178719138</v>
       </c>
       <c r="GA17" t="n">
         <v>0.3208816373264634</v>
@@ -12825,7 +12825,7 @@
         <v>25.39366197183095</v>
       </c>
       <c r="HV17" t="n">
-        <v>0.2748456984506865</v>
+        <v>0.2776385058912008</v>
       </c>
     </row>
     <row r="18">
@@ -12869,19 +12869,19 @@
         <v>-681</v>
       </c>
       <c r="J18" t="n">
-        <v>8194</v>
+        <v>8225</v>
       </c>
       <c r="K18" t="n">
-        <v>8252</v>
+        <v>8221</v>
       </c>
       <c r="L18" t="n">
-        <v>1889</v>
+        <v>1915</v>
       </c>
       <c r="M18" t="n">
-        <v>2229</v>
+        <v>2205</v>
       </c>
       <c r="N18" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="O18" t="n">
         <v>16446</v>
@@ -13229,7 +13229,7 @@
         <v>2177</v>
       </c>
       <c r="DZ18" t="n">
-        <v>1875</v>
+        <v>1901</v>
       </c>
       <c r="EA18" t="n">
         <v>158</v>
@@ -13376,16 +13376,16 @@
         <v>0.6053333333333333</v>
       </c>
       <c r="FW18" t="n">
-        <v>14.85501586526727</v>
+        <v>14.7990273556231</v>
       </c>
       <c r="FX18" t="n">
-        <v>13.94062045564712</v>
+        <v>13.99318817662085</v>
       </c>
       <c r="FY18" t="n">
-        <v>14.25324627776422</v>
+        <v>14.19952583586626</v>
       </c>
       <c r="FZ18" t="n">
-        <v>13.35548957828405</v>
+        <v>13.40585086972388</v>
       </c>
       <c r="GA18" t="n">
         <v>0.2603140803832845</v>
@@ -13529,7 +13529,7 @@
         <v>25.33869263783427</v>
       </c>
       <c r="HV18" t="n">
-        <v>0.2305345374664389</v>
+        <v>0.2328267477203647</v>
       </c>
     </row>
     <row r="19">
@@ -13573,19 +13573,19 @@
         <v>691</v>
       </c>
       <c r="J19" t="n">
-        <v>8459</v>
+        <v>8486</v>
       </c>
       <c r="K19" t="n">
-        <v>8521</v>
+        <v>8494</v>
       </c>
       <c r="L19" t="n">
-        <v>2418</v>
+        <v>2441</v>
       </c>
       <c r="M19" t="n">
-        <v>2269</v>
+        <v>2243</v>
       </c>
       <c r="N19" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="O19" t="n">
         <v>16980</v>
@@ -13931,7 +13931,7 @@
         <v>2899</v>
       </c>
       <c r="DZ19" t="n">
-        <v>2403</v>
+        <v>2426</v>
       </c>
       <c r="EA19" t="n">
         <v>144</v>
@@ -14076,16 +14076,16 @@
         <v>0.5660377358490566</v>
       </c>
       <c r="FW19" t="n">
-        <v>13.96520865350514</v>
+        <v>13.92077539476785</v>
       </c>
       <c r="FX19" t="n">
-        <v>14.06270390799202</v>
+        <v>14.10740522721921</v>
       </c>
       <c r="FY19" t="n">
-        <v>13.3943610355834</v>
+        <v>13.35174404902192</v>
       </c>
       <c r="FZ19" t="n">
-        <v>13.50197159957751</v>
+        <v>13.54489051094891</v>
       </c>
       <c r="GA19" t="n">
         <v>0.244775722081725</v>
@@ -14229,7 +14229,7 @@
         <v>25.43046573716998</v>
       </c>
       <c r="HV19" t="n">
-        <v>0.2858493911809907</v>
+        <v>0.2876502474664153</v>
       </c>
     </row>
     <row r="20">
@@ -14273,19 +14273,19 @@
         <v>-144</v>
       </c>
       <c r="J20" t="n">
-        <v>8067</v>
+        <v>8090</v>
       </c>
       <c r="K20" t="n">
-        <v>8119</v>
+        <v>8096</v>
       </c>
       <c r="L20" t="n">
-        <v>1786</v>
+        <v>1801</v>
       </c>
       <c r="M20" t="n">
-        <v>2234</v>
+        <v>2216</v>
       </c>
       <c r="N20" t="n">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="O20" t="n">
         <v>16186</v>
@@ -14633,7 +14633,7 @@
         <v>2153</v>
       </c>
       <c r="DZ20" t="n">
-        <v>1777</v>
+        <v>1792</v>
       </c>
       <c r="EA20" t="n">
         <v>170</v>
@@ -14780,16 +14780,16 @@
         <v>0.607773851590106</v>
       </c>
       <c r="FW20" t="n">
-        <v>14.40864013883724</v>
+        <v>14.3676761433869</v>
       </c>
       <c r="FX20" t="n">
-        <v>14.80791969454366</v>
+        <v>14.84998764822134</v>
       </c>
       <c r="FY20" t="n">
-        <v>13.81025164249411</v>
+        <v>13.77098887515451</v>
       </c>
       <c r="FZ20" t="n">
-        <v>14.30083754156916</v>
+        <v>14.34146492094862</v>
       </c>
       <c r="GA20" t="n">
         <v>0.2802811078958247</v>
@@ -14933,7 +14933,7 @@
         <v>25.7041918175721</v>
       </c>
       <c r="HV20" t="n">
-        <v>0.2213958100904921</v>
+        <v>0.2226205191594561</v>
       </c>
     </row>
     <row r="21">
@@ -14968,7 +14968,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>237660</v>
+        <v>237663</v>
       </c>
       <c r="H21" t="n">
         <v>82</v>
@@ -14977,19 +14977,19 @@
         <v>46</v>
       </c>
       <c r="J21" t="n">
-        <v>8158</v>
+        <v>8186</v>
       </c>
       <c r="K21" t="n">
-        <v>8222</v>
+        <v>8194</v>
       </c>
       <c r="L21" t="n">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="M21" t="n">
-        <v>1927</v>
+        <v>1900</v>
       </c>
       <c r="N21" t="n">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="O21" t="n">
         <v>16380</v>
@@ -15337,7 +15337,7 @@
         <v>2436</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2043</v>
+        <v>2067</v>
       </c>
       <c r="EA21" t="n">
         <v>126</v>
@@ -15478,22 +15478,22 @@
         <v>0.04982415005861664</v>
       </c>
       <c r="FU21" t="n">
-        <v>99.24766473112851</v>
+        <v>99.24641193622902</v>
       </c>
       <c r="FV21" t="n">
         <v>0.5701754385964912</v>
       </c>
       <c r="FW21" t="n">
-        <v>14.10224319686198</v>
+        <v>14.05400684094796</v>
       </c>
       <c r="FX21" t="n">
-        <v>14.9129044028217</v>
+        <v>14.96422992433488</v>
       </c>
       <c r="FY21" t="n">
-        <v>13.47248100024516</v>
+        <v>13.42639872953824</v>
       </c>
       <c r="FZ21" t="n">
-        <v>14.27771831671126</v>
+        <v>14.32687332194288</v>
       </c>
       <c r="GA21" t="n">
         <v>0.2578694158075601</v>
@@ -15637,7 +15637,7 @@
         <v>25.72569680489463</v>
       </c>
       <c r="HV21" t="n">
-        <v>0.2515322382936994</v>
+        <v>0.253603713657464</v>
       </c>
     </row>
     <row r="22">
@@ -15681,19 +15681,19 @@
         <v>-914</v>
       </c>
       <c r="J22" t="n">
-        <v>8213</v>
+        <v>8238</v>
       </c>
       <c r="K22" t="n">
-        <v>8267</v>
+        <v>8242</v>
       </c>
       <c r="L22" t="n">
-        <v>1935</v>
+        <v>1954</v>
       </c>
       <c r="M22" t="n">
-        <v>1971</v>
+        <v>1955</v>
       </c>
       <c r="N22" t="n">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="O22" t="n">
         <v>16480</v>
@@ -16041,7 +16041,7 @@
         <v>2119</v>
       </c>
       <c r="DZ22" t="n">
-        <v>1930</v>
+        <v>1949</v>
       </c>
       <c r="EA22" t="n">
         <v>143</v>
@@ -16188,16 +16188,16 @@
         <v>0.5921787709497207</v>
       </c>
       <c r="FW22" t="n">
-        <v>14.94035066358213</v>
+        <v>14.89501092498179</v>
       </c>
       <c r="FX22" t="n">
-        <v>13.97785169952824</v>
+        <v>14.02024993933511</v>
       </c>
       <c r="FY22" t="n">
-        <v>14.2704492877146</v>
+        <v>14.22714251031804</v>
       </c>
       <c r="FZ22" t="n">
-        <v>13.44608685133664</v>
+        <v>13.48687211841786</v>
       </c>
       <c r="GA22" t="n">
         <v>0.25161201810948</v>
@@ -16341,7 +16341,7 @@
         <v>25.30943869551584</v>
       </c>
       <c r="HV22" t="n">
-        <v>0.2356020942408377</v>
+        <v>0.2371934935663996</v>
       </c>
     </row>
     <row r="23">
@@ -16385,19 +16385,19 @@
         <v>-428</v>
       </c>
       <c r="J23" t="n">
-        <v>7956</v>
+        <v>7982</v>
       </c>
       <c r="K23" t="n">
-        <v>8006</v>
+        <v>7980</v>
       </c>
       <c r="L23" t="n">
-        <v>1712</v>
+        <v>1735</v>
       </c>
       <c r="M23" t="n">
-        <v>2081</v>
+        <v>2056</v>
       </c>
       <c r="N23" t="n">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="O23" t="n">
         <v>15962</v>
@@ -16745,7 +16745,7 @@
         <v>1903</v>
       </c>
       <c r="DZ23" t="n">
-        <v>1695</v>
+        <v>1718</v>
       </c>
       <c r="EA23" t="n">
         <v>176</v>
@@ -16892,16 +16892,16 @@
         <v>0.5246753246753246</v>
       </c>
       <c r="FW23" t="n">
-        <v>14.24928355957768</v>
+        <v>14.20286895514909</v>
       </c>
       <c r="FX23" t="n">
-        <v>15.67483137646765</v>
+        <v>15.7259022556391</v>
       </c>
       <c r="FY23" t="n">
-        <v>13.60972850678733</v>
+        <v>13.56539714357304</v>
       </c>
       <c r="FZ23" t="n">
-        <v>14.84822633025231</v>
+        <v>14.89660401002506</v>
       </c>
       <c r="GA23" t="n">
         <v>0.2662811510395153</v>
@@ -17045,7 +17045,7 @@
         <v>25.65174680041508</v>
       </c>
       <c r="HV23" t="n">
-        <v>0.2151835093011564</v>
+        <v>0.2173640691556001</v>
       </c>
     </row>
     <row r="24">
@@ -17089,19 +17089,19 @@
         <v>-198</v>
       </c>
       <c r="J24" t="n">
-        <v>8347</v>
+        <v>8371</v>
       </c>
       <c r="K24" t="n">
-        <v>8407</v>
+        <v>8383</v>
       </c>
       <c r="L24" t="n">
-        <v>2015</v>
+        <v>2032</v>
       </c>
       <c r="M24" t="n">
-        <v>1880</v>
+        <v>1860</v>
       </c>
       <c r="N24" t="n">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="O24" t="n">
         <v>16754</v>
@@ -17447,7 +17447,7 @@
         <v>2253</v>
       </c>
       <c r="DZ24" t="n">
-        <v>1992</v>
+        <v>2009</v>
       </c>
       <c r="EA24" t="n">
         <v>122</v>
@@ -17594,16 +17594,16 @@
         <v>0.599502487562189</v>
       </c>
       <c r="FW24" t="n">
-        <v>14.71973164011022</v>
+        <v>14.67752956636005</v>
       </c>
       <c r="FX24" t="n">
-        <v>13.58325205186154</v>
+        <v>13.62214004532983</v>
       </c>
       <c r="FY24" t="n">
-        <v>14.1431412483527</v>
+        <v>14.10259228288138</v>
       </c>
       <c r="FZ24" t="n">
-        <v>13.01032472939217</v>
+        <v>13.04757246809018</v>
       </c>
       <c r="GA24" t="n">
         <v>0.3116689280868385</v>
@@ -17747,7 +17747,7 @@
         <v>25.42044384667115</v>
       </c>
       <c r="HV24" t="n">
-        <v>0.2414040972804601</v>
+        <v>0.2427428025325529</v>
       </c>
     </row>
     <row r="25">
@@ -17791,19 +17791,19 @@
         <v>-631</v>
       </c>
       <c r="J25" t="n">
-        <v>7764</v>
+        <v>7799</v>
       </c>
       <c r="K25" t="n">
-        <v>7846</v>
+        <v>7811</v>
       </c>
       <c r="L25" t="n">
-        <v>1699</v>
+        <v>1726</v>
       </c>
       <c r="M25" t="n">
-        <v>1792</v>
+        <v>1761</v>
       </c>
       <c r="N25" t="n">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="O25" t="n">
         <v>15610</v>
@@ -18149,7 +18149,7 @@
         <v>1904</v>
       </c>
       <c r="DZ25" t="n">
-        <v>1682</v>
+        <v>1709</v>
       </c>
       <c r="EA25" t="n">
         <v>112</v>
@@ -18296,16 +18296,16 @@
         <v>0.5339233038348082</v>
       </c>
       <c r="FW25" t="n">
-        <v>14.6379057187017</v>
+        <v>14.5722143864598</v>
       </c>
       <c r="FX25" t="n">
-        <v>15.69096354830487</v>
+        <v>15.76127256433235</v>
       </c>
       <c r="FY25" t="n">
-        <v>13.97660999484802</v>
+        <v>13.91388639569175</v>
       </c>
       <c r="FZ25" t="n">
-        <v>14.88414478715269</v>
+        <v>14.95083856100371</v>
       </c>
       <c r="GA25" t="n">
         <v>0.2081877881794048</v>
@@ -18449,7 +18449,7 @@
         <v>25.71539900249376</v>
       </c>
       <c r="HV25" t="n">
-        <v>0.2188304997424008</v>
+        <v>0.2213104244133863</v>
       </c>
     </row>
     <row r="26">
@@ -18493,16 +18493,16 @@
         <v>-338</v>
       </c>
       <c r="J26" t="n">
-        <v>8204</v>
+        <v>8230</v>
       </c>
       <c r="K26" t="n">
-        <v>8270</v>
+        <v>8244</v>
       </c>
       <c r="L26" t="n">
-        <v>2141</v>
+        <v>2161</v>
       </c>
       <c r="M26" t="n">
-        <v>2294</v>
+        <v>2278</v>
       </c>
       <c r="N26" t="n">
         <v>986</v>
@@ -18851,7 +18851,7 @@
         <v>2454</v>
       </c>
       <c r="DZ26" t="n">
-        <v>2129</v>
+        <v>2149</v>
       </c>
       <c r="EA26" t="n">
         <v>171</v>
@@ -18998,16 +18998,16 @@
         <v>0.5903954802259888</v>
       </c>
       <c r="FW26" t="n">
-        <v>14.86413944417357</v>
+        <v>14.81718104495747</v>
       </c>
       <c r="FX26" t="n">
-        <v>13.91954050785973</v>
+        <v>13.96344007763222</v>
       </c>
       <c r="FY26" t="n">
-        <v>14.20433934666016</v>
+        <v>14.15946537059538</v>
       </c>
       <c r="FZ26" t="n">
-        <v>13.23935912938331</v>
+        <v>13.2811135371179</v>
       </c>
       <c r="GA26" t="n">
         <v>0.2800762112139358</v>
@@ -19151,7 +19151,7 @@
         <v>25.65156749840051</v>
       </c>
       <c r="HV26" t="n">
-        <v>0.2609702584105315</v>
+        <v>0.2625759416767922</v>
       </c>
     </row>
     <row r="27">
@@ -19195,19 +19195,19 @@
         <v>427</v>
       </c>
       <c r="J27" t="n">
-        <v>8407</v>
+        <v>8436</v>
       </c>
       <c r="K27" t="n">
-        <v>8468</v>
+        <v>8439</v>
       </c>
       <c r="L27" t="n">
-        <v>2039</v>
+        <v>2064</v>
       </c>
       <c r="M27" t="n">
-        <v>2118</v>
+        <v>2091</v>
       </c>
       <c r="N27" t="n">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="O27" t="n">
         <v>16875</v>
@@ -19553,7 +19553,7 @@
         <v>2420</v>
       </c>
       <c r="DZ27" t="n">
-        <v>2023</v>
+        <v>2048</v>
       </c>
       <c r="EA27" t="n">
         <v>130</v>
@@ -19700,16 +19700,16 @@
         <v>0.6214442013129103</v>
       </c>
       <c r="FW27" t="n">
-        <v>14.43930058284763</v>
+        <v>14.38966334755808</v>
       </c>
       <c r="FX27" t="n">
-        <v>13.65951818611242</v>
+        <v>13.70645811115061</v>
       </c>
       <c r="FY27" t="n">
-        <v>13.8527417628167</v>
+        <v>13.80512091038407</v>
       </c>
       <c r="FZ27" t="n">
-        <v>13.07549598488427</v>
+        <v>13.12042896077734</v>
       </c>
       <c r="GA27" t="n">
         <v>0.3216647218980941</v>
@@ -19853,7 +19853,7 @@
         <v>25.42423371647509</v>
       </c>
       <c r="HV27" t="n">
-        <v>0.2425359819198287</v>
+        <v>0.2446657183499289</v>
       </c>
     </row>
     <row r="28">
@@ -19897,19 +19897,19 @@
         <v>-191</v>
       </c>
       <c r="J28" t="n">
-        <v>8473</v>
+        <v>8506</v>
       </c>
       <c r="K28" t="n">
-        <v>8517</v>
+        <v>8484</v>
       </c>
       <c r="L28" t="n">
-        <v>2188</v>
+        <v>2219</v>
       </c>
       <c r="M28" t="n">
-        <v>2289</v>
+        <v>2262</v>
       </c>
       <c r="N28" t="n">
-        <v>1021</v>
+        <v>1026</v>
       </c>
       <c r="O28" t="n">
         <v>16990</v>
@@ -20255,7 +20255,7 @@
         <v>2487</v>
       </c>
       <c r="DZ28" t="n">
-        <v>2174</v>
+        <v>2205</v>
       </c>
       <c r="EA28" t="n">
         <v>125</v>
@@ -20402,16 +20402,16 @@
         <v>0.6004962779156328</v>
       </c>
       <c r="FW28" t="n">
-        <v>14.75084385695739</v>
+        <v>14.69361627086762</v>
       </c>
       <c r="FX28" t="n">
-        <v>13.08865797816133</v>
+        <v>13.13956859971712</v>
       </c>
       <c r="FY28" t="n">
-        <v>14.14418741885991</v>
+        <v>14.08931342581707</v>
       </c>
       <c r="FZ28" t="n">
-        <v>12.51997182106376</v>
+        <v>12.56867043847242</v>
       </c>
       <c r="GA28" t="n">
         <v>0.2711134316668842</v>
@@ -20555,7 +20555,7 @@
         <v>25.56188242651657</v>
       </c>
       <c r="HV28" t="n">
-        <v>0.2582320311577954</v>
+        <v>0.2608746766988008</v>
       </c>
     </row>
     <row r="29">
@@ -20599,19 +20599,19 @@
         <v>-519</v>
       </c>
       <c r="J29" t="n">
-        <v>7959</v>
+        <v>7986</v>
       </c>
       <c r="K29" t="n">
-        <v>8013</v>
+        <v>7986</v>
       </c>
       <c r="L29" t="n">
-        <v>1932</v>
+        <v>1955</v>
       </c>
       <c r="M29" t="n">
-        <v>1814</v>
+        <v>1795</v>
       </c>
       <c r="N29" t="n">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="O29" t="n">
         <v>15972</v>
@@ -20957,7 +20957,7 @@
         <v>2185</v>
       </c>
       <c r="DZ29" t="n">
-        <v>1915</v>
+        <v>1938</v>
       </c>
       <c r="EA29" t="n">
         <v>104</v>
@@ -21104,16 +21104,16 @@
         <v>0.5211267605633803</v>
       </c>
       <c r="FW29" t="n">
-        <v>14.54447794949114</v>
+        <v>14.49530428249436</v>
       </c>
       <c r="FX29" t="n">
-        <v>15.13796330962187</v>
+        <v>15.18914350112697</v>
       </c>
       <c r="FY29" t="n">
-        <v>13.96537253423797</v>
+        <v>13.91815677435512</v>
       </c>
       <c r="FZ29" t="n">
-        <v>14.46756520653937</v>
+        <v>14.51647883796644</v>
       </c>
       <c r="GA29" t="n">
         <v>0.2763120567375886</v>
@@ -21257,7 +21257,7 @@
         <v>25.39726550079491</v>
       </c>
       <c r="HV29" t="n">
-        <v>0.2427440633245383</v>
+        <v>0.2448034059604308</v>
       </c>
     </row>
     <row r="30">
@@ -21301,19 +21301,19 @@
         <v>-52</v>
       </c>
       <c r="J30" t="n">
-        <v>8227</v>
+        <v>8257</v>
       </c>
       <c r="K30" t="n">
-        <v>8280</v>
+        <v>8250</v>
       </c>
       <c r="L30" t="n">
-        <v>2273</v>
+        <v>2301</v>
       </c>
       <c r="M30" t="n">
-        <v>2438</v>
+        <v>2411</v>
       </c>
       <c r="N30" t="n">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="O30" t="n">
         <v>16507</v>
@@ -21659,7 +21659,7 @@
         <v>2626</v>
       </c>
       <c r="DZ30" t="n">
-        <v>2266</v>
+        <v>2294</v>
       </c>
       <c r="EA30" t="n">
         <v>171</v>
@@ -21806,16 +21806,16 @@
         <v>0.5565610859728507</v>
       </c>
       <c r="FW30" t="n">
-        <v>14.44063449617114</v>
+        <v>14.38816761535667</v>
       </c>
       <c r="FX30" t="n">
-        <v>14.39092995169082</v>
+        <v>14.4432606060606</v>
       </c>
       <c r="FY30" t="n">
-        <v>13.86974595842956</v>
+        <v>13.81935327600824</v>
       </c>
       <c r="FZ30" t="n">
-        <v>13.77618357487923</v>
+        <v>13.82627878787879</v>
       </c>
       <c r="GA30" t="n">
         <v>0.2765486725663717</v>
@@ -21959,7 +21959,7 @@
         <v>25.55862068965517</v>
       </c>
       <c r="HV30" t="n">
-        <v>0.2762854017260241</v>
+        <v>0.2786726413951798</v>
       </c>
     </row>
     <row r="31">
@@ -21994,7 +21994,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>237059.7</v>
+        <v>237060</v>
       </c>
       <c r="H31" t="n">
         <v>82</v>
@@ -22003,19 +22003,19 @@
         <v>-120</v>
       </c>
       <c r="J31" t="n">
-        <v>8000</v>
+        <v>8019</v>
       </c>
       <c r="K31" t="n">
-        <v>8063</v>
+        <v>8044</v>
       </c>
       <c r="L31" t="n">
-        <v>2052</v>
+        <v>2068</v>
       </c>
       <c r="M31" t="n">
-        <v>1803</v>
+        <v>1789</v>
       </c>
       <c r="N31" t="n">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="O31" t="n">
         <v>16063</v>
@@ -22363,7 +22363,7 @@
         <v>2327</v>
       </c>
       <c r="DZ31" t="n">
-        <v>2040</v>
+        <v>2056</v>
       </c>
       <c r="EA31" t="n">
         <v>127</v>
@@ -22504,22 +22504,22 @@
         <v>0.05252100840336135</v>
       </c>
       <c r="FU31" t="n">
-        <v>97.57339606858524</v>
+        <v>97.57327258921792</v>
       </c>
       <c r="FV31" t="n">
         <v>0.5765027322404371</v>
       </c>
       <c r="FW31" t="n">
-        <v>14.877</v>
+        <v>14.84175084175084</v>
       </c>
       <c r="FX31" t="n">
-        <v>14.64017115217661</v>
+        <v>14.67478866235704</v>
       </c>
       <c r="FY31" t="n">
-        <v>14.245375</v>
+        <v>14.21162239680758</v>
       </c>
       <c r="FZ31" t="n">
-        <v>13.92072429616768</v>
+        <v>13.95364246643461</v>
       </c>
       <c r="GA31" t="n">
         <v>0.2775967124840584</v>
@@ -22663,7 +22663,7 @@
         <v>25.65714782608696</v>
       </c>
       <c r="HV31" t="n">
-        <v>0.2565</v>
+        <v>0.2578875171467764</v>
       </c>
     </row>
   </sheetData>
